--- a/lab 13/data.xlsx
+++ b/lab 13/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\邱\Documents\Labsforclaude\lab 13\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\邱\Documents\Labsforothers\lab 13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5ED9AC-B169-4F47-A4F4-FE79601ED8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457490E0-3DF3-45BA-AAA1-F65F24A5809E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F8BD8D5E-73AD-4184-9804-B86894EFFB58}"/>
   </bookViews>
@@ -535,8 +535,8 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -544,50 +544,50 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4">
+      <c r="B2" s="4">
         <v>7.44</v>
       </c>
-      <c r="D2">
+      <c r="C2" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E2">
         <v>390000</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2">
-        <v>18.399999999999999</v>
-      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="J2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
@@ -595,99 +595,99 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4">
+      <c r="B3" s="4">
         <v>7.89</v>
       </c>
-      <c r="D3">
+      <c r="C3">
+        <v>20.2</v>
+      </c>
+      <c r="E3">
         <v>390000</v>
       </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>20.2</v>
+      <c r="G3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4">
+      <c r="B4" s="4">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="C4" s="2">
+        <v>22</v>
+      </c>
+      <c r="E4">
         <v>390000</v>
       </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2">
-        <v>22</v>
+      <c r="G4">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4">
+      <c r="B5" s="4">
         <v>10.130000000000001</v>
       </c>
-      <c r="D5">
+      <c r="C5" s="2">
+        <v>24.8</v>
+      </c>
+      <c r="E5">
         <v>390000</v>
       </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="I5" s="2">
-        <v>24.8</v>
+      <c r="G5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4">
+      <c r="B6" s="4">
         <v>11.2</v>
       </c>
-      <c r="D6">
+      <c r="C6">
+        <v>27.4</v>
+      </c>
+      <c r="E6">
         <v>390000</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>27.4</v>
+      <c r="G6">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7"/>
+      <c r="B7">
+        <v>12.02</v>
+      </c>
       <c r="C7">
-        <v>12.02</v>
-      </c>
-      <c r="D7">
+        <v>29.2</v>
+      </c>
+      <c r="E7">
         <v>390000</v>
       </c>
-      <c r="E7"/>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7"/>
+      <c r="F7"/>
+      <c r="G7">
+        <v>5</v>
+      </c>
       <c r="H7"/>
-      <c r="I7">
-        <v>29.2</v>
-      </c>
+      <c r="I7"/>
+      <c r="J7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3">
+      <c r="B8" s="3">
         <v>1.9600000000000003E-2</v>
       </c>
-      <c r="I8">
+      <c r="C8">
         <v>10.199999999999999</v>
       </c>
     </row>
@@ -695,10 +695,10 @@
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3">
+      <c r="B9" s="3">
         <v>2.7800000000000002E-2</v>
       </c>
-      <c r="I9">
+      <c r="C9">
         <v>13.8</v>
       </c>
     </row>
@@ -706,10 +706,10 @@
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3">
+      <c r="B10" s="3">
         <v>4.3299999999999998E-2</v>
       </c>
-      <c r="I10">
+      <c r="C10">
         <v>22.2</v>
       </c>
     </row>
@@ -717,10 +717,10 @@
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3">
+      <c r="B11" s="3">
         <v>5.3200000000000004E-2</v>
       </c>
-      <c r="I11">
+      <c r="C11">
         <v>27.4</v>
       </c>
     </row>
@@ -728,10 +728,10 @@
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="3">
+      <c r="B12" s="3">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="I12">
+      <c r="C12">
         <v>30.8</v>
       </c>
     </row>
@@ -739,78 +739,78 @@
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13">
-        <v>5</v>
+      <c r="C13">
+        <v>28.2</v>
       </c>
       <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
         <v>150</v>
       </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
         <v>1.65</v>
       </c>
-      <c r="H13">
-        <v>5</v>
-      </c>
       <c r="I13">
-        <v>28.2</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14">
+      <c r="C14">
+        <v>27.8</v>
+      </c>
+      <c r="D14">
+        <v>3.22</v>
+      </c>
+      <c r="E14">
+        <v>300</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>17</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
         <v>1</v>
-      </c>
-      <c r="D14">
-        <v>300</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1">
-        <v>17</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
-      <c r="I14">
-        <v>27.8</v>
-      </c>
-      <c r="J14">
-        <v>3.22</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="C15">
+        <v>26.2</v>
+      </c>
+      <c r="D15">
+        <v>3.11</v>
+      </c>
+      <c r="E15">
+        <v>150</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
         <v>0.5</v>
-      </c>
-      <c r="D15">
-        <v>150</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="G15">
-        <v>16</v>
-      </c>
-      <c r="H15">
-        <v>5</v>
-      </c>
-      <c r="I15">
-        <v>26.2</v>
-      </c>
-      <c r="J15">
-        <v>3.11</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -818,285 +818,285 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="C16">
-        <v>4.95</v>
-      </c>
-      <c r="D16">
+        <v>23.2</v>
+      </c>
+      <c r="E16">
         <v>150</v>
       </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
         <v>200000</v>
       </c>
-      <c r="H16">
-        <v>5</v>
-      </c>
       <c r="I16">
-        <v>23.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B17">
+        <v>1.4970000000000001</v>
+      </c>
+      <c r="C17">
+        <v>28.2</v>
+      </c>
+      <c r="E17">
+        <v>150</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>50000</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
         <v>1.5</v>
       </c>
-      <c r="C17">
-        <v>1.4970000000000001</v>
-      </c>
-      <c r="D17">
-        <v>150</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-      <c r="G17" s="1">
-        <v>50000</v>
-      </c>
-      <c r="H17">
-        <v>5</v>
-      </c>
-      <c r="I17">
-        <v>28.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B18">
+        <v>0.4</v>
+      </c>
       <c r="C18">
-        <v>0.4</v>
-      </c>
-      <c r="D18" s="1">
+        <v>44.2</v>
+      </c>
+      <c r="E18" s="1">
         <v>390</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>386</v>
       </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
       <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
         <v>6200</v>
       </c>
-      <c r="H18">
-        <v>5</v>
-      </c>
       <c r="I18">
-        <v>44.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B19">
+        <v>0.4</v>
+      </c>
       <c r="C19">
-        <v>0.4</v>
-      </c>
-      <c r="D19" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="E19" s="1">
         <v>39000</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>39200</v>
       </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
       <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
         <v>6200</v>
       </c>
-      <c r="H19">
-        <v>5</v>
-      </c>
       <c r="I19">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B20">
+        <v>0.4</v>
+      </c>
       <c r="C20">
-        <v>0.4</v>
-      </c>
-      <c r="D20" s="1">
-        <v>390000</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="1">
         <v>390000</v>
       </c>
-      <c r="F20">
-        <v>5</v>
+      <c r="F20" s="1">
+        <v>390000</v>
       </c>
       <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
         <v>6200</v>
       </c>
-      <c r="H20">
-        <v>5</v>
-      </c>
       <c r="I20">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B21">
+        <v>2.0299999999999998</v>
+      </c>
       <c r="C21">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="D21" s="1">
+        <v>49.4</v>
+      </c>
+      <c r="E21" s="1">
         <v>390</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>386</v>
       </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
       <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21">
         <v>39000</v>
       </c>
-      <c r="H21">
-        <v>5</v>
-      </c>
       <c r="I21">
-        <v>49.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B22">
+        <v>2.0299999999999998</v>
+      </c>
       <c r="C22">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="D22" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="E22" s="1">
         <v>39000</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>39200</v>
       </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
       <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
         <v>39000</v>
       </c>
-      <c r="H22">
-        <v>5</v>
-      </c>
       <c r="I22">
-        <v>24.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B23">
+        <v>2.0299999999999998</v>
+      </c>
       <c r="C23">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="D23" s="1">
-        <v>390000</v>
+        <v>4.2</v>
       </c>
       <c r="E23" s="1">
         <v>390000</v>
       </c>
-      <c r="F23">
-        <v>5</v>
+      <c r="F23" s="1">
+        <v>390000</v>
       </c>
       <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23">
         <v>39000</v>
       </c>
-      <c r="H23">
-        <v>5</v>
-      </c>
       <c r="I23">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B24">
+        <v>10.09</v>
+      </c>
       <c r="C24">
-        <v>10.09</v>
-      </c>
-      <c r="D24" s="1">
+        <v>46</v>
+      </c>
+      <c r="E24" s="1">
         <v>390</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>386</v>
       </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
       <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
         <v>200000</v>
       </c>
-      <c r="H24">
-        <v>5</v>
-      </c>
       <c r="I24">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B25">
+        <v>10.09</v>
+      </c>
       <c r="C25">
-        <v>10.09</v>
-      </c>
-      <c r="D25" s="1">
+        <v>38.6</v>
+      </c>
+      <c r="E25" s="1">
         <v>39000</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>39200</v>
       </c>
-      <c r="F25">
-        <v>5</v>
-      </c>
       <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
         <v>200000</v>
       </c>
-      <c r="H25">
-        <v>5</v>
-      </c>
       <c r="I25">
-        <v>38.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B26">
+        <v>10.09</v>
+      </c>
       <c r="C26">
-        <v>10.09</v>
-      </c>
-      <c r="D26" s="1">
-        <v>390000</v>
+        <v>15.6</v>
       </c>
       <c r="E26" s="1">
         <v>390000</v>
       </c>
-      <c r="F26">
-        <v>5</v>
+      <c r="F26" s="1">
+        <v>390000</v>
       </c>
       <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
         <v>200000</v>
       </c>
-      <c r="H26">
-        <v>5</v>
-      </c>
       <c r="I26">
-        <v>15.6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
